--- a/artfynd/A 18984-2026 artfynd.xlsx
+++ b/artfynd/A 18984-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>131048434</v>
+        <v>131048367</v>
       </c>
       <c r="B2" t="n">
-        <v>57076</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>465647</v>
+        <v>465783</v>
       </c>
       <c r="R2" t="n">
-        <v>6780895</v>
+        <v>6780977</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,6 +774,312 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>131048434</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Blyberg-Våmhus-Fryksås, Dlr</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>465647</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6780895</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Petter Westberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petter Westberg, Kasper Wieck, Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>131048435</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Blyberg-Våmhus-Fryksås, Dlr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>465537</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6780761</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petter Westberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petter Westberg, Kasper Wieck, Martin Berg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>131048617</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Blyberg-Våmhus-Fryksås, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>465615</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6780943</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Våmhus</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-12</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petter Westberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petter Westberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
